--- a/artfynd/A 39569-2022 artfynd.xlsx
+++ b/artfynd/A 39569-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39569-2022 artfynd.xlsx
+++ b/artfynd/A 39569-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111506847</v>
+        <v>111526230</v>
       </c>
       <c r="B2" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Berget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459174.3706188269</v>
+        <v>459138</v>
       </c>
       <c r="R2" t="n">
-        <v>6374077.693022936</v>
+        <v>6374187</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111528636</v>
+        <v>111506847</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,28 +784,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,13 +818,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459136.55025383</v>
+        <v>459174</v>
       </c>
       <c r="R3" t="n">
-        <v>6374171.016094602</v>
+        <v>6374077</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,29 +848,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -915,54 +880,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111526230</v>
+        <v>111528636</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Berget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459138.32674584</v>
+        <v>459137</v>
       </c>
       <c r="R4" t="n">
-        <v>6374187.115417362</v>
+        <v>6374171</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,26 +954,16 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1025,6 +980,314 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108286602</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Berget, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>459123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6373854</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svenarum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111524787</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Berget, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>459064</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6374175</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svenarum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108323547</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Berget, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>459089</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6373816</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svenarum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39569-2022 artfynd.xlsx
+++ b/artfynd/A 39569-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111526230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111506847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108286602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111524787</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108323547</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>